--- a/BD_Hinterland.xlsx
+++ b/BD_Hinterland.xlsx
@@ -29291,8 +29291,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="4b8b536fcb9f2c664ed0fa8e4c5bcaeb">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9c3fb262092b4aec5ef66bdd34acef6e" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
     <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
     <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
     <xsd:element name="properties">
@@ -29491,6 +29491,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03AC95AB-53AE-4403-BA35-6CB23B248E1A}">
   <ds:schemaRefs>
@@ -29500,20 +29511,9 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A324110-5727-4458-84EF-57AEDA9FF05B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <ds:schemaRef ds:uri="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B2DD63D-C27B-473B-ABF4-5CA9621C5A04}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F551F34-A0DE-4DBF-901D-1C18C05E293C}"/>
 </file>